--- a/data/questions.xlsx
+++ b/data/questions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>What is a stochastic expriment?</t>
+          <t>What are unitary matrices?</t>
         </is>
       </c>
       <c r="B2" t="b">
@@ -441,10 +441,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>What do you mean by metaphysical systems?</t>
+          <t>What are Metamaterials?</t>
         </is>
       </c>
       <c r="B3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>What is Nanotechnology?</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/questions.xlsx
+++ b/data/questions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,6 +458,24 @@
         <v>1</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
